--- a/students_data.xlsx
+++ b/students_data.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ahmed\Desktop\ExamApp\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pat\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="152">
   <si>
     <t>كود المعلم</t>
   </si>
@@ -288,6 +288,198 @@
   </si>
   <si>
     <t>امنيه سرور عبد العظيم سرور</t>
+  </si>
+  <si>
+    <t>أحمد جمال على البوهي</t>
+  </si>
+  <si>
+    <t>احمد محمد سيد حسين</t>
+  </si>
+  <si>
+    <t>حسام الدين احمد جمال كامل</t>
+  </si>
+  <si>
+    <t>روضه خميس احمد علي سعد</t>
+  </si>
+  <si>
+    <t>وفاء سعيد محمد عوض</t>
+  </si>
+  <si>
+    <t>داليا محمد عبدالغفار محمد</t>
+  </si>
+  <si>
+    <t>دميان نظير نسيم عطوان</t>
+  </si>
+  <si>
+    <t>ماهر هلال خيرى محمد</t>
+  </si>
+  <si>
+    <t>محمد هلال محمد امام</t>
+  </si>
+  <si>
+    <t>عبد الرحمن هشام مصطفى فاضل</t>
+  </si>
+  <si>
+    <t>احمد سعيد احمد محمد</t>
+  </si>
+  <si>
+    <t>روماني عصام صليب حنا</t>
+  </si>
+  <si>
+    <t>هويدا على عوض الله محمد</t>
+  </si>
+  <si>
+    <t>رحاب عصام عزيز على</t>
+  </si>
+  <si>
+    <t>هناء مصطفى عبد الباقى عبد الجواد</t>
+  </si>
+  <si>
+    <t>ايه وحيد حسنى سيد</t>
+  </si>
+  <si>
+    <t>فاطمه فايز حجاج اسماعيل</t>
+  </si>
+  <si>
+    <t>شيماء محمد محمد حسانين</t>
+  </si>
+  <si>
+    <t>محمود بيومي محمود بيومي</t>
+  </si>
+  <si>
+    <t>نعمه يونس محمد يونس</t>
+  </si>
+  <si>
+    <t>عبد الله محمد احمد سنهابى</t>
+  </si>
+  <si>
+    <t>هبه عبد العال عبد الحميد علي</t>
+  </si>
+  <si>
+    <t>نعيمة جمال ربيع مكاوي</t>
+  </si>
+  <si>
+    <t>خلود عصام فاروق عبدالحميد</t>
+  </si>
+  <si>
+    <t>اسامه عبد الرازق عبدالله حطب</t>
+  </si>
+  <si>
+    <t>رانيا حسن محمد محمود</t>
+  </si>
+  <si>
+    <t>رمضان عيد ابراهيم مسعود</t>
+  </si>
+  <si>
+    <t>احمد شريف احمد محمد</t>
+  </si>
+  <si>
+    <t>هاجر سعدالدين عوض محمد</t>
+  </si>
+  <si>
+    <t>ايمان حسن محمد حسين</t>
+  </si>
+  <si>
+    <t>بسنت ايهاب ابراهيم طنطاوي</t>
+  </si>
+  <si>
+    <t>اسماء محمد عبد التواب عبد المحسن</t>
+  </si>
+  <si>
+    <t>محمد رضا رمضان محمد</t>
+  </si>
+  <si>
+    <t>ريهام مبروك عبد العزيز محمود</t>
+  </si>
+  <si>
+    <t>شيماء راغب فكري راغب</t>
+  </si>
+  <si>
+    <t>سارة طه عبد المنعم احمد</t>
+  </si>
+  <si>
+    <t>فاطمة محمد على محمد</t>
+  </si>
+  <si>
+    <t>عمر سيد كمال عبدالحفيظ الشريف</t>
+  </si>
+  <si>
+    <t>مصطفى عرفه حماده محمد حسان</t>
+  </si>
+  <si>
+    <t>امنيه هلال عبدالله محمد</t>
+  </si>
+  <si>
+    <t>محمد عبدالنبى سيد احمد</t>
+  </si>
+  <si>
+    <t>عمرو محمود محمد احمد</t>
+  </si>
+  <si>
+    <t>ايه شاذلى حسن حامد</t>
+  </si>
+  <si>
+    <t>كريم كرم جلال خميس</t>
+  </si>
+  <si>
+    <t>أحمد سعودي سيد احمد سعودي</t>
+  </si>
+  <si>
+    <t>احمد صالح محمد على خاطر</t>
+  </si>
+  <si>
+    <t>على طه على امام بسيونى</t>
+  </si>
+  <si>
+    <t>هبه سعيد محمد امام</t>
+  </si>
+  <si>
+    <t>احمد ابوالحسن محمد عبداللطيف</t>
+  </si>
+  <si>
+    <t>اميره محمود حسين اسماعيل علي</t>
+  </si>
+  <si>
+    <t>اسراء محمد عبدالتواب عبدالجواد</t>
+  </si>
+  <si>
+    <t>علاء محمود السيد عبد المعبود</t>
+  </si>
+  <si>
+    <t>عماد نشات عبد الله حسين</t>
+  </si>
+  <si>
+    <t>ايه محمد حسين دسوقي</t>
+  </si>
+  <si>
+    <t>عبير محمد محمود عيسى</t>
+  </si>
+  <si>
+    <t>عليه محمد عيد محمد</t>
+  </si>
+  <si>
+    <t>لمياء كمال احمد محمد</t>
+  </si>
+  <si>
+    <t>دعاء رضا عبدالرحمن محمد</t>
+  </si>
+  <si>
+    <t>شروق احمد على سيد احمد بحيرى</t>
+  </si>
+  <si>
+    <t>عمرو فراج محمد سلامة</t>
+  </si>
+  <si>
+    <t>نورهان وجدى سعد احمد</t>
+  </si>
+  <si>
+    <t>عبد الله جمال سيد مرزوق</t>
+  </si>
+  <si>
+    <t>محمد ثروت بدر عبدالجواد</t>
+  </si>
+  <si>
+    <t>محمد إسماعيل محمد السيد</t>
   </si>
 </sst>
 </file>
@@ -298,7 +490,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -319,7 +511,7 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -466,7 +658,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -510,6 +702,18 @@
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="22" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="22" fontId="1" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -793,18 +997,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G77"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G141"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="26.75" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15" style="15" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="25.5" customWidth="1"/>
-    <col min="5" max="5" width="15.875" customWidth="1"/>
-    <col min="6" max="6" width="13.375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="47.28515625" customWidth="1"/>
+    <col min="3" max="3" width="27.42578125" style="15" customWidth="1"/>
+    <col min="4" max="4" width="39.28515625" customWidth="1"/>
+    <col min="5" max="5" width="15.85546875" customWidth="1"/>
+    <col min="6" max="6" width="17.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -824,7 +1028,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
         <v>2905298</v>
       </c>
@@ -844,7 +1048,7 @@
         <v>46266.5625</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6">
         <v>3779340</v>
       </c>
@@ -864,7 +1068,7 @@
         <v>46266.560416666667</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6">
         <v>3681300</v>
       </c>
@@ -884,7 +1088,7 @@
         <v>46266.517361111109</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
         <v>3681261</v>
       </c>
@@ -904,7 +1108,7 @@
         <v>46266.517361111109</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
         <v>3681362</v>
       </c>
@@ -924,7 +1128,7 @@
         <v>46266.51666666667</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
         <v>3779208</v>
       </c>
@@ -944,7 +1148,7 @@
         <v>46266.51458333333</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
         <v>3695367</v>
       </c>
@@ -964,7 +1168,7 @@
         <v>46266.498611111114</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
         <v>3778045</v>
       </c>
@@ -984,7 +1188,7 @@
         <v>46266.496527777781</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
         <v>3681751</v>
       </c>
@@ -1004,7 +1208,7 @@
         <v>46266.495138888888</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
         <v>3685896</v>
       </c>
@@ -1024,7 +1228,7 @@
         <v>46266.484722222223</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
         <v>3778323</v>
       </c>
@@ -1044,7 +1248,7 @@
         <v>46266.481249999997</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
         <v>3769964</v>
       </c>
@@ -1064,7 +1268,7 @@
         <v>46266.479166666664</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
         <v>3710664</v>
       </c>
@@ -1084,7 +1288,7 @@
         <v>46266.475694444445</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
         <v>3769950</v>
       </c>
@@ -1104,7 +1308,7 @@
         <v>46266.473611111112</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6">
         <v>3776079</v>
       </c>
@@ -1124,7 +1328,7 @@
         <v>46266.472222222219</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
         <v>3783231</v>
       </c>
@@ -1144,7 +1348,7 @@
         <v>46266.470833333333</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="6">
         <v>3787770</v>
       </c>
@@ -1164,7 +1368,7 @@
         <v>46266.467361111114</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="6">
         <v>380438</v>
       </c>
@@ -1184,7 +1388,7 @@
         <v>46266.457638888889</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="6">
         <v>3777237</v>
       </c>
@@ -1204,7 +1408,7 @@
         <v>46266.45</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="6">
         <v>3779492</v>
       </c>
@@ -1224,7 +1428,7 @@
         <v>46266.445138888892</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="6">
         <v>3781555</v>
       </c>
@@ -1244,7 +1448,7 @@
         <v>46266.441666666666</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="6">
         <v>3780992</v>
       </c>
@@ -1264,7 +1468,7 @@
         <v>46266.440972222219</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6">
         <v>3722520</v>
       </c>
@@ -1284,7 +1488,7 @@
         <v>46266.438888888886</v>
       </c>
     </row>
-    <row r="25" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="6">
         <v>3769960</v>
       </c>
@@ -1304,7 +1508,7 @@
         <v>46266.438888888886</v>
       </c>
     </row>
-    <row r="26" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="6">
         <v>3778370</v>
       </c>
@@ -1324,7 +1528,7 @@
         <v>46266.436805555553</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="6">
         <v>627713</v>
       </c>
@@ -1344,7 +1548,7 @@
         <v>46266.423611111109</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="6">
         <v>3778046</v>
       </c>
@@ -1364,7 +1568,7 @@
         <v>46266.423611111109</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="6">
         <v>3778338</v>
       </c>
@@ -1384,7 +1588,7 @@
         <v>46266.42291666667</v>
       </c>
     </row>
-    <row r="30" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="6">
         <v>3769069</v>
       </c>
@@ -1404,7 +1608,7 @@
         <v>46266.422222222223</v>
       </c>
     </row>
-    <row r="31" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="6">
         <v>3710592</v>
       </c>
@@ -1424,7 +1628,7 @@
         <v>46266.421527777777</v>
       </c>
     </row>
-    <row r="32" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="6">
         <v>3689182</v>
       </c>
@@ -1444,7 +1648,7 @@
         <v>46266.418055555558</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="6">
         <v>3778344</v>
       </c>
@@ -1462,7 +1666,7 @@
       </c>
       <c r="F33" s="1"/>
     </row>
-    <row r="34" spans="1:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="6">
         <v>3733556</v>
       </c>
@@ -1480,7 +1684,7 @@
       </c>
       <c r="F34" s="1"/>
     </row>
-    <row r="35" spans="1:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="6">
         <v>1498970</v>
       </c>
@@ -1498,7 +1702,7 @@
       </c>
       <c r="F35" s="1"/>
     </row>
-    <row r="36" spans="1:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="6">
         <v>3787193</v>
       </c>
@@ -1516,7 +1720,7 @@
       </c>
       <c r="F36" s="1"/>
     </row>
-    <row r="37" spans="1:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="6">
         <v>3787194</v>
       </c>
@@ -1534,7 +1738,7 @@
       </c>
       <c r="F37" s="1"/>
     </row>
-    <row r="38" spans="1:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="6">
         <v>3693746</v>
       </c>
@@ -1552,7 +1756,7 @@
       </c>
       <c r="F38" s="1"/>
     </row>
-    <row r="39" spans="1:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="6">
         <v>3787206</v>
       </c>
@@ -1570,7 +1774,7 @@
       </c>
       <c r="F39" s="1"/>
     </row>
-    <row r="40" spans="1:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="6">
         <v>3787181</v>
       </c>
@@ -1588,7 +1792,7 @@
       </c>
       <c r="F40" s="1"/>
     </row>
-    <row r="41" spans="1:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:7" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="8">
         <v>3787192</v>
       </c>
@@ -1606,7 +1810,7 @@
       </c>
       <c r="F41" s="9"/>
     </row>
-    <row r="42" spans="1:7" ht="33" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A42" s="8">
         <v>3687850</v>
       </c>
@@ -1627,7 +1831,7 @@
       </c>
       <c r="G42" s="16"/>
     </row>
-    <row r="43" spans="1:7" ht="33" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A43" s="8">
         <v>3687845</v>
       </c>
@@ -1648,7 +1852,7 @@
       </c>
       <c r="G43" s="7"/>
     </row>
-    <row r="44" spans="1:7" ht="33" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A44" s="8">
         <v>3687847</v>
       </c>
@@ -1669,7 +1873,7 @@
       </c>
       <c r="G44" s="7"/>
     </row>
-    <row r="45" spans="1:7" ht="33" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A45" s="8">
         <v>3681349</v>
       </c>
@@ -1690,7 +1894,7 @@
       </c>
       <c r="G45" s="7"/>
     </row>
-    <row r="46" spans="1:7" ht="33" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A46" s="8">
         <v>3706475</v>
       </c>
@@ -1711,7 +1915,7 @@
       </c>
       <c r="G46" s="7"/>
     </row>
-    <row r="47" spans="1:7" ht="33" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A47" s="8">
         <v>3705667</v>
       </c>
@@ -1732,7 +1936,7 @@
       </c>
       <c r="G47" s="7"/>
     </row>
-    <row r="48" spans="1:7" ht="33" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A48" s="8">
         <v>3698460</v>
       </c>
@@ -1753,7 +1957,7 @@
       </c>
       <c r="G48" s="7"/>
     </row>
-    <row r="49" spans="1:7" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A49" s="8">
         <v>2397499</v>
       </c>
@@ -1774,7 +1978,7 @@
       </c>
       <c r="G49" s="7"/>
     </row>
-    <row r="50" spans="1:7" ht="33" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A50" s="8">
         <v>3723857</v>
       </c>
@@ -1795,7 +1999,7 @@
       </c>
       <c r="G50" s="7"/>
     </row>
-    <row r="51" spans="1:7" ht="33" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A51" s="8">
         <v>3781990</v>
       </c>
@@ -1816,7 +2020,7 @@
       </c>
       <c r="G51" s="7"/>
     </row>
-    <row r="52" spans="1:7" ht="33" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A52" s="8">
         <v>3663134</v>
       </c>
@@ -1837,7 +2041,7 @@
       </c>
       <c r="G52" s="7"/>
     </row>
-    <row r="53" spans="1:7" ht="33" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A53" s="8">
         <v>3779390</v>
       </c>
@@ -1858,7 +2062,7 @@
       </c>
       <c r="G53" s="7"/>
     </row>
-    <row r="54" spans="1:7" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A54" s="8">
         <v>2157890</v>
       </c>
@@ -1879,7 +2083,7 @@
       </c>
       <c r="G54" s="7"/>
     </row>
-    <row r="55" spans="1:7" ht="33" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A55" s="8">
         <v>3663140</v>
       </c>
@@ -1900,7 +2104,7 @@
       </c>
       <c r="G55" s="7"/>
     </row>
-    <row r="56" spans="1:7" ht="33" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A56" s="8">
         <v>3704814</v>
       </c>
@@ -1921,7 +2125,7 @@
       </c>
       <c r="G56" s="7"/>
     </row>
-    <row r="57" spans="1:7" ht="33" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A57" s="8">
         <v>3686142</v>
       </c>
@@ -1942,7 +2146,7 @@
       </c>
       <c r="G57" s="7"/>
     </row>
-    <row r="58" spans="1:7" ht="33" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A58" s="8">
         <v>3698684</v>
       </c>
@@ -1963,7 +2167,7 @@
       </c>
       <c r="G58" s="7"/>
     </row>
-    <row r="59" spans="1:7" ht="33" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A59" s="8">
         <v>3722445</v>
       </c>
@@ -1984,7 +2188,7 @@
       </c>
       <c r="G59" s="7"/>
     </row>
-    <row r="60" spans="1:7" ht="33" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A60" s="8">
         <v>3722428</v>
       </c>
@@ -2005,7 +2209,7 @@
       </c>
       <c r="G60" s="7"/>
     </row>
-    <row r="61" spans="1:7" ht="33" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A61" s="8">
         <v>3697356</v>
       </c>
@@ -2026,7 +2230,7 @@
       </c>
       <c r="G61" s="7"/>
     </row>
-    <row r="62" spans="1:7" ht="33" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A62" s="8">
         <v>3781554</v>
       </c>
@@ -2047,7 +2251,7 @@
       </c>
       <c r="G62" s="7"/>
     </row>
-    <row r="63" spans="1:7" ht="33" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A63" s="8">
         <v>3780420</v>
       </c>
@@ -2068,7 +2272,7 @@
       </c>
       <c r="G63" s="7"/>
     </row>
-    <row r="64" spans="1:7" ht="33" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A64" s="8">
         <v>3778329</v>
       </c>
@@ -2089,7 +2293,7 @@
       </c>
       <c r="G64" s="7"/>
     </row>
-    <row r="65" spans="1:7" ht="33" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A65" s="8">
         <v>3778327</v>
       </c>
@@ -2110,7 +2314,7 @@
       </c>
       <c r="G65" s="7"/>
     </row>
-    <row r="66" spans="1:7" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A66" s="8">
         <v>384762</v>
       </c>
@@ -2131,7 +2335,7 @@
       </c>
       <c r="G66" s="7"/>
     </row>
-    <row r="67" spans="1:7" ht="33" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A67" s="8">
         <v>3779651</v>
       </c>
@@ -2152,7 +2356,7 @@
       </c>
       <c r="G67" s="7"/>
     </row>
-    <row r="68" spans="1:7" ht="33" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A68" s="8">
         <v>3778361</v>
       </c>
@@ -2173,7 +2377,7 @@
       </c>
       <c r="G68" s="7"/>
     </row>
-    <row r="69" spans="1:7" ht="33" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A69" s="8">
         <v>3679700</v>
       </c>
@@ -2194,7 +2398,7 @@
       </c>
       <c r="G69" s="7"/>
     </row>
-    <row r="70" spans="1:7" ht="33" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A70" s="8">
         <v>3778343</v>
       </c>
@@ -2215,7 +2419,7 @@
       </c>
       <c r="G70" s="7"/>
     </row>
-    <row r="71" spans="1:7" ht="33" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A71" s="8">
         <v>3660831</v>
       </c>
@@ -2236,7 +2440,7 @@
       </c>
       <c r="G71" s="7"/>
     </row>
-    <row r="72" spans="1:7" ht="33" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A72" s="8">
         <v>3670643</v>
       </c>
@@ -2257,7 +2461,7 @@
       </c>
       <c r="G72" s="7"/>
     </row>
-    <row r="73" spans="1:7" ht="33" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A73" s="8">
         <v>3770150</v>
       </c>
@@ -2278,7 +2482,7 @@
       </c>
       <c r="G73" s="7"/>
     </row>
-    <row r="74" spans="1:7" ht="33" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A74" s="8">
         <v>3719325</v>
       </c>
@@ -2299,7 +2503,7 @@
       </c>
       <c r="G74" s="7"/>
     </row>
-    <row r="75" spans="1:7" ht="33" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A75" s="8">
         <v>3778342</v>
       </c>
@@ -2320,7 +2524,7 @@
       </c>
       <c r="G75" s="7"/>
     </row>
-    <row r="76" spans="1:7" ht="33" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:7" ht="33" x14ac:dyDescent="0.25">
       <c r="A76" s="8">
         <v>3779653</v>
       </c>
@@ -2341,7 +2545,7 @@
       </c>
       <c r="G76" s="7"/>
     </row>
-    <row r="77" spans="1:7" ht="33" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A77" s="8">
         <v>3783603</v>
       </c>
@@ -2361,6 +2565,1350 @@
         <v>46267.396527777775</v>
       </c>
       <c r="G77" s="11"/>
+    </row>
+    <row r="78" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A78" s="17">
+        <v>3699978</v>
+      </c>
+      <c r="B78" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="C78" s="14">
+        <v>29611281700039</v>
+      </c>
+      <c r="D78" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="E78" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F78" s="19">
+        <v>46268.487500000003</v>
+      </c>
+      <c r="G78" s="16"/>
+    </row>
+    <row r="79" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A79" s="6">
+        <v>3786644</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C79" s="14">
+        <v>29709272500639</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E79" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F79" s="2">
+        <v>46268.484722222223</v>
+      </c>
+      <c r="G79" s="7"/>
+    </row>
+    <row r="80" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A80" s="6">
+        <v>3722537</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C80" s="14">
+        <v>29501012138251</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E80" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F80" s="2">
+        <v>46268.46597222222</v>
+      </c>
+      <c r="G80" s="7"/>
+    </row>
+    <row r="81" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A81" s="6">
+        <v>3787207</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C81" s="14">
+        <v>29801110200724</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E81" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F81" s="2">
+        <v>46268.465277777781</v>
+      </c>
+      <c r="G81" s="7"/>
+    </row>
+    <row r="82" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A82" s="6">
+        <v>3728848</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C82" s="14">
+        <v>28812082301241</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E82" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F82" s="2">
+        <v>46268.464583333334</v>
+      </c>
+      <c r="G82" s="7"/>
+    </row>
+    <row r="83" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A83" s="6">
+        <v>3685135</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C83" s="14">
+        <v>30010012101287</v>
+      </c>
+      <c r="D83" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E83" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F83" s="2">
+        <v>46268.463888888888</v>
+      </c>
+      <c r="G83" s="7"/>
+    </row>
+    <row r="84" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A84" s="6">
+        <v>3778325</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C84" s="14">
+        <v>28508122600512</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E84" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F84" s="2">
+        <v>46268.463194444441</v>
+      </c>
+      <c r="G84" s="7"/>
+    </row>
+    <row r="85" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A85" s="6">
+        <v>3779486</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C85" s="14">
+        <v>28705022601031</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E85" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F85" s="2">
+        <v>46268.462500000001</v>
+      </c>
+      <c r="G85" s="7"/>
+    </row>
+    <row r="86" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A86" s="6">
+        <v>3685126</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C86" s="14">
+        <v>29808102106039</v>
+      </c>
+      <c r="D86" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E86" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F86" s="2">
+        <v>46268.461111111108</v>
+      </c>
+      <c r="G86" s="7"/>
+    </row>
+    <row r="87" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A87" s="6">
+        <v>3446729</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C87" s="14">
+        <v>30010010122392</v>
+      </c>
+      <c r="D87" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E87" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F87" s="2">
+        <v>46268.459027777775</v>
+      </c>
+      <c r="G87" s="7"/>
+    </row>
+    <row r="88" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A88" s="6">
+        <v>3683509</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C88" s="14">
+        <v>29210292102091</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E88" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F88" s="2">
+        <v>46268.459027777775</v>
+      </c>
+      <c r="G88" s="7"/>
+    </row>
+    <row r="89" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A89" s="6">
+        <v>3695798</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C89" s="14">
+        <v>29611012106619</v>
+      </c>
+      <c r="D89" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E89" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F89" s="2">
+        <v>46268.459027777775</v>
+      </c>
+      <c r="G89" s="7"/>
+    </row>
+    <row r="90" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A90" s="6">
+        <v>3778249</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C90" s="14">
+        <v>28906132800183</v>
+      </c>
+      <c r="D90" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E90" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F90" s="2">
+        <v>46268.445138888892</v>
+      </c>
+      <c r="G90" s="7"/>
+    </row>
+    <row r="91" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A91" s="6">
+        <v>3703851</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C91" s="14">
+        <v>29501162301509</v>
+      </c>
+      <c r="D91" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E91" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F91" s="2">
+        <v>46268.440972222219</v>
+      </c>
+      <c r="G91" s="7"/>
+    </row>
+    <row r="92" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A92" s="6">
+        <v>3769226</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C92" s="14">
+        <v>29612102101523</v>
+      </c>
+      <c r="D92" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E92" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F92" s="2">
+        <v>46268.439583333333</v>
+      </c>
+      <c r="G92" s="7"/>
+    </row>
+    <row r="93" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A93" s="6">
+        <v>3722533</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C93" s="14">
+        <v>29710012205186</v>
+      </c>
+      <c r="D93" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E93" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F93" s="2">
+        <v>46268.4375</v>
+      </c>
+      <c r="G93" s="7"/>
+    </row>
+    <row r="94" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A94" s="6">
+        <v>3772832</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C94" s="14">
+        <v>30109232101322</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E94" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F94" s="2">
+        <v>46268.4375</v>
+      </c>
+      <c r="G94" s="7"/>
+    </row>
+    <row r="95" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A95" s="6">
+        <v>3686568</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C95" s="14">
+        <v>29807062100087</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E95" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F95" s="2">
+        <v>46268.436805555553</v>
+      </c>
+      <c r="G95" s="7"/>
+    </row>
+    <row r="96" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A96" s="6">
+        <v>3694335</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C96" s="14">
+        <v>29210012123756</v>
+      </c>
+      <c r="D96" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E96" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F96" s="2">
+        <v>46268.436805555553</v>
+      </c>
+      <c r="G96" s="7"/>
+    </row>
+    <row r="97" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A97" s="6">
+        <v>3769973</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C97" s="14">
+        <v>29711252800789</v>
+      </c>
+      <c r="D97" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E97" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F97" s="2">
+        <v>46268.436111111114</v>
+      </c>
+      <c r="G97" s="7"/>
+    </row>
+    <row r="98" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A98" s="6">
+        <v>3720215</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C98" s="14">
+        <v>29603252302072</v>
+      </c>
+      <c r="D98" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E98" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F98" s="2">
+        <v>46268.436111111114</v>
+      </c>
+      <c r="G98" s="7"/>
+    </row>
+    <row r="99" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A99" s="6">
+        <v>3782945</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C99" s="14">
+        <v>29404272300146</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E99" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F99" s="2">
+        <v>46268.435416666667</v>
+      </c>
+      <c r="G99" s="7"/>
+    </row>
+    <row r="100" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A100" s="6">
+        <v>3787184</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="C100" s="14">
+        <v>29408162101666</v>
+      </c>
+      <c r="D100" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E100" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F100" s="2">
+        <v>46268.435416666667</v>
+      </c>
+      <c r="G100" s="7"/>
+    </row>
+    <row r="101" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A101" s="6">
+        <v>3778713</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C101" s="14">
+        <v>29709202102504</v>
+      </c>
+      <c r="D101" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E101" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F101" s="2">
+        <v>46268.43472222222</v>
+      </c>
+      <c r="G101" s="7"/>
+    </row>
+    <row r="102" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A102" s="6">
+        <v>3787699</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C102" s="14">
+        <v>28604031701391</v>
+      </c>
+      <c r="D102" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E102" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F102" s="2">
+        <v>46268.434027777781</v>
+      </c>
+      <c r="G102" s="7"/>
+    </row>
+    <row r="103" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A103" s="6">
+        <v>3685053</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C103" s="14">
+        <v>29109302107301</v>
+      </c>
+      <c r="D103" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E103" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F103" s="2">
+        <v>46268.433333333334</v>
+      </c>
+      <c r="G103" s="7"/>
+    </row>
+    <row r="104" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A104" s="6">
+        <v>3685419</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C104" s="14">
+        <v>29702012105651</v>
+      </c>
+      <c r="D104" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E104" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F104" s="2">
+        <v>46268.433333333334</v>
+      </c>
+      <c r="G104" s="7"/>
+    </row>
+    <row r="105" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A105" s="6">
+        <v>3777948</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C105" s="14">
+        <v>30108062100338</v>
+      </c>
+      <c r="D105" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E105" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F105" s="2">
+        <v>46268.433333333334</v>
+      </c>
+      <c r="G105" s="7"/>
+    </row>
+    <row r="106" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A106" s="6">
+        <v>3677770</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C106" s="14">
+        <v>29903012113462</v>
+      </c>
+      <c r="D106" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E106" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F106" s="2">
+        <v>46268.432638888888</v>
+      </c>
+      <c r="G106" s="7"/>
+    </row>
+    <row r="107" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A107" s="6">
+        <v>3782634</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="C107" s="14">
+        <v>28907162102541</v>
+      </c>
+      <c r="D107" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E107" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F107" s="2">
+        <v>46268.431944444441</v>
+      </c>
+      <c r="G107" s="7"/>
+    </row>
+    <row r="108" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A108" s="6">
+        <v>3778352</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C108" s="14">
+        <v>30203280104046</v>
+      </c>
+      <c r="D108" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E108" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F108" s="2">
+        <v>46268.42291666667</v>
+      </c>
+      <c r="G108" s="7"/>
+    </row>
+    <row r="109" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A109" s="6">
+        <v>3769413</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="C109" s="14">
+        <v>30008202105446</v>
+      </c>
+      <c r="D109" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E109" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F109" s="2">
+        <v>46268.42291666667</v>
+      </c>
+      <c r="G109" s="7"/>
+    </row>
+    <row r="110" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A110" s="6">
+        <v>3787653</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C110" s="14">
+        <v>29906242102515</v>
+      </c>
+      <c r="D110" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E110" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F110" s="2">
+        <v>46268.419444444444</v>
+      </c>
+      <c r="G110" s="7"/>
+    </row>
+    <row r="111" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A111" s="6">
+        <v>3778251</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C111" s="14">
+        <v>29107102101128</v>
+      </c>
+      <c r="D111" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E111" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F111" s="2">
+        <v>46268.418055555558</v>
+      </c>
+      <c r="G111" s="7"/>
+    </row>
+    <row r="112" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A112" s="6">
+        <v>3778345</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="C112" s="14">
+        <v>29411102103563</v>
+      </c>
+      <c r="D112" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E112" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F112" s="2">
+        <v>46268.418055555558</v>
+      </c>
+      <c r="G112" s="7"/>
+    </row>
+    <row r="113" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A113" s="6">
+        <v>3778350</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="C113" s="14">
+        <v>29111122100346</v>
+      </c>
+      <c r="D113" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E113" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F113" s="2">
+        <v>46268.417361111111</v>
+      </c>
+      <c r="G113" s="7"/>
+    </row>
+    <row r="114" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A114" s="6">
+        <v>3665271</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="C114" s="14">
+        <v>29410012126941</v>
+      </c>
+      <c r="D114" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E114" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F114" s="2">
+        <v>46268.416666666664</v>
+      </c>
+      <c r="G114" s="7"/>
+    </row>
+    <row r="115" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A115" s="6">
+        <v>3684888</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C115" s="14">
+        <v>29311142101275</v>
+      </c>
+      <c r="D115" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E115" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F115" s="2">
+        <v>46268.416666666664</v>
+      </c>
+      <c r="G115" s="7"/>
+    </row>
+    <row r="116" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A116" s="6">
+        <v>3684895</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C116" s="14">
+        <v>28412062100097</v>
+      </c>
+      <c r="D116" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E116" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F116" s="2">
+        <v>46268.415972222225</v>
+      </c>
+      <c r="G116" s="7"/>
+    </row>
+    <row r="117" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A117" s="6">
+        <v>3682116</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="C117" s="14">
+        <v>29901202301408</v>
+      </c>
+      <c r="D117" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E117" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F117" s="2">
+        <v>46268.415972222225</v>
+      </c>
+      <c r="G117" s="7"/>
+    </row>
+    <row r="118" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A118" s="6">
+        <v>3722500</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C118" s="14">
+        <v>30007240104775</v>
+      </c>
+      <c r="D118" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E118" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F118" s="2">
+        <v>46268.415972222225</v>
+      </c>
+      <c r="G118" s="7"/>
+    </row>
+    <row r="119" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A119" s="6">
+        <v>3787652</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C119" s="14">
+        <v>29607272502375</v>
+      </c>
+      <c r="D119" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E119" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F119" s="2">
+        <v>46268.415972222225</v>
+      </c>
+      <c r="G119" s="7"/>
+    </row>
+    <row r="120" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A120" s="6">
+        <v>3780862</v>
+      </c>
+      <c r="B120" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="C120" s="14">
+        <v>29606202104643</v>
+      </c>
+      <c r="D120" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E120" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F120" s="2">
+        <v>46268.413888888892</v>
+      </c>
+      <c r="G120" s="7"/>
+    </row>
+    <row r="121" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A121" s="6">
+        <v>3692512</v>
+      </c>
+      <c r="B121" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C121" s="14">
+        <v>29808212100052</v>
+      </c>
+      <c r="D121" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E121" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F121" s="2">
+        <v>46268.412499999999</v>
+      </c>
+      <c r="G121" s="7"/>
+    </row>
+    <row r="122" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A122" s="6">
+        <v>3681179</v>
+      </c>
+      <c r="B122" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="C122" s="14">
+        <v>29806022102579</v>
+      </c>
+      <c r="D122" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E122" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F122" s="2">
+        <v>46268.412499999999</v>
+      </c>
+      <c r="G122" s="7"/>
+    </row>
+    <row r="123" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A123" s="6">
+        <v>3684923</v>
+      </c>
+      <c r="B123" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="C123" s="14">
+        <v>30102212103758</v>
+      </c>
+      <c r="D123" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E123" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F123" s="2">
+        <v>46268.412499999999</v>
+      </c>
+      <c r="G123" s="7"/>
+    </row>
+    <row r="124" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A124" s="6">
+        <v>3688082</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="C124" s="14">
+        <v>30006262102656</v>
+      </c>
+      <c r="D124" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E124" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F124" s="2">
+        <v>46268.411805555559</v>
+      </c>
+      <c r="G124" s="7"/>
+    </row>
+    <row r="125" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A125" s="6">
+        <v>3682359</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="C125" s="14">
+        <v>30005112103186</v>
+      </c>
+      <c r="D125" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E125" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F125" s="2">
+        <v>46268.406944444447</v>
+      </c>
+      <c r="G125" s="7"/>
+    </row>
+    <row r="126" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A126" s="6">
+        <v>1686338</v>
+      </c>
+      <c r="B126" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="C126" s="14">
+        <v>27512292600031</v>
+      </c>
+      <c r="D126" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E126" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F126" s="2">
+        <v>46268.40625</v>
+      </c>
+      <c r="G126" s="7"/>
+    </row>
+    <row r="127" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A127" s="6">
+        <v>3708286</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="C127" s="14">
+        <v>29511092101448</v>
+      </c>
+      <c r="D127" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E127" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F127" s="2">
+        <v>46268.40625</v>
+      </c>
+      <c r="G127" s="7"/>
+    </row>
+    <row r="128" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A128" s="6">
+        <v>3685026</v>
+      </c>
+      <c r="B128" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C128" s="14">
+        <v>29606012112224</v>
+      </c>
+      <c r="D128" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E128" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F128" s="2">
+        <v>46268.405555555553</v>
+      </c>
+      <c r="G128" s="7"/>
+    </row>
+    <row r="129" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A129" s="6">
+        <v>2369528</v>
+      </c>
+      <c r="B129" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="C129" s="14">
+        <v>27610252103656</v>
+      </c>
+      <c r="D129" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E129" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F129" s="2">
+        <v>46268.405555555553</v>
+      </c>
+      <c r="G129" s="7"/>
+    </row>
+    <row r="130" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A130" s="6">
+        <v>1587360</v>
+      </c>
+      <c r="B130" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="C130" s="14">
+        <v>27301202104551</v>
+      </c>
+      <c r="D130" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E130" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F130" s="2">
+        <v>46268.404861111114</v>
+      </c>
+      <c r="G130" s="7"/>
+    </row>
+    <row r="131" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A131" s="6">
+        <v>3679547</v>
+      </c>
+      <c r="B131" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="C131" s="14">
+        <v>30010282104261</v>
+      </c>
+      <c r="D131" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E131" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F131" s="2">
+        <v>46268.404861111114</v>
+      </c>
+      <c r="G131" s="7"/>
+    </row>
+    <row r="132" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A132" s="6">
+        <v>3696395</v>
+      </c>
+      <c r="B132" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="C132" s="14">
+        <v>28802242601542</v>
+      </c>
+      <c r="D132" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E132" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F132" s="2">
+        <v>46268.404166666667</v>
+      </c>
+      <c r="G132" s="7"/>
+    </row>
+    <row r="133" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A133" s="6">
+        <v>3722525</v>
+      </c>
+      <c r="B133" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C133" s="14">
+        <v>29507302102348</v>
+      </c>
+      <c r="D133" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E133" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F133" s="2">
+        <v>46268.404166666667</v>
+      </c>
+      <c r="G133" s="7"/>
+    </row>
+    <row r="134" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A134" s="6">
+        <v>3700506</v>
+      </c>
+      <c r="B134" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="C134" s="14">
+        <v>28402072602583</v>
+      </c>
+      <c r="D134" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E134" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F134" s="2">
+        <v>46268.40347222222</v>
+      </c>
+      <c r="G134" s="7"/>
+    </row>
+    <row r="135" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A135" s="6">
+        <v>3696044</v>
+      </c>
+      <c r="B135" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="C135" s="14">
+        <v>29004112101866</v>
+      </c>
+      <c r="D135" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E135" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F135" s="2">
+        <v>46268.40347222222</v>
+      </c>
+      <c r="G135" s="7"/>
+    </row>
+    <row r="136" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A136" s="6">
+        <v>3696040</v>
+      </c>
+      <c r="B136" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="C136" s="14">
+        <v>29905312101744</v>
+      </c>
+      <c r="D136" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E136" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F136" s="2">
+        <v>46268.402083333334</v>
+      </c>
+      <c r="G136" s="7"/>
+    </row>
+    <row r="137" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A137" s="6">
+        <v>3787650</v>
+      </c>
+      <c r="B137" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="C137" s="14">
+        <v>29604272101355</v>
+      </c>
+      <c r="D137" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E137" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F137" s="2">
+        <v>46268.402083333334</v>
+      </c>
+      <c r="G137" s="7"/>
+    </row>
+    <row r="138" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A138" s="6">
+        <v>3778358</v>
+      </c>
+      <c r="B138" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="C138" s="14">
+        <v>29012032102627</v>
+      </c>
+      <c r="D138" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E138" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F138" s="2">
+        <v>46268.4</v>
+      </c>
+      <c r="G138" s="7"/>
+    </row>
+    <row r="139" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A139" s="6">
+        <v>3770777</v>
+      </c>
+      <c r="B139" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="C139" s="14">
+        <v>28702012408731</v>
+      </c>
+      <c r="D139" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E139" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F139" s="2">
+        <v>46268.397916666669</v>
+      </c>
+      <c r="G139" s="7"/>
+    </row>
+    <row r="140" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A140" s="6">
+        <v>3688931</v>
+      </c>
+      <c r="B140" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="C140" s="14">
+        <v>29407102501855</v>
+      </c>
+      <c r="D140" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E140" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F140" s="2">
+        <v>46268.397916666669</v>
+      </c>
+      <c r="G140" s="7"/>
+    </row>
+    <row r="141" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A141" s="8">
+        <v>2221429</v>
+      </c>
+      <c r="B141" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="C141" s="14">
+        <v>28401222104998</v>
+      </c>
+      <c r="D141" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="E141" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F141" s="20">
+        <v>46268.397222222222</v>
+      </c>
+      <c r="G141" s="11"/>
     </row>
   </sheetData>
   <hyperlinks>
